--- a/Uploads/Data/Datalogger/SS_SemiAnnual_ShellBudget_WQ.xlsx
+++ b/Uploads/Data/Datalogger/SS_SemiAnnual_ShellBudget_WQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fwc-spfs1\FishBio\Molluscs\Oysters\NFWF2.0\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\Datalogger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1902FD-D9D7-4148-B7AB-73D1B55D6BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9365126-2166-49CD-A93C-F7A018B3A97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{ECA94287-1607-4690-AA42-F1104461785C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ECA94287-1607-4690-AA42-F1104461785C}"/>
   </bookViews>
   <sheets>
     <sheet name="WQ" sheetId="1" r:id="rId1"/>
@@ -770,24 +770,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D6DE35-7571-488C-BCE8-8E8CC322ADCF}">
-  <dimension ref="A1:S73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="30"/>
-    <col min="12" max="12" width="8.88671875" style="30"/>
-    <col min="13" max="13" width="13.44140625" style="31" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="30"/>
-    <col min="15" max="15" width="11.77734375" style="30" customWidth="1"/>
-    <col min="16" max="17" width="8.88671875" style="30"/>
-    <col min="18" max="18" width="13.5546875" customWidth="1"/>
-    <col min="21" max="21" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="30"/>
+    <col min="12" max="12" width="8.85546875" style="30"/>
+    <col min="13" max="13" width="13.42578125" style="31" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="30"/>
+    <col min="15" max="15" width="11.7109375" style="30" customWidth="1"/>
+    <col min="16" max="17" width="8.85546875" style="30"/>
+    <col min="18" max="18" width="13.5703125" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -808,7 +808,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -829,7 +829,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:18" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -850,7 +850,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:18" s="7" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -867,7 +867,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:18" s="15" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>1</v>
       </c>
@@ -923,7 +923,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>21</v>
       </c>
@@ -979,7 +979,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>21</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>21</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>21</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>21</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>21</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>21</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>21</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>21</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>21</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>21</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>21</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>21</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>21</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>21</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>21</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>21</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>21</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>21</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>21</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>21</v>
       </c>
@@ -1945,11 +1945,63 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="29">
+        <v>45188</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30">
+        <v>29.227070000000001</v>
+      </c>
+      <c r="I30">
+        <v>83.134839999999997</v>
+      </c>
+      <c r="J30" s="30">
+        <v>1.75</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30" s="30">
+        <v>1.75</v>
+      </c>
+      <c r="M30" s="31">
+        <v>27.9</v>
+      </c>
+      <c r="N30" s="30">
+        <v>20.260000000000002</v>
+      </c>
+      <c r="O30" s="30">
+        <v>5.73</v>
+      </c>
+      <c r="P30" s="30">
+        <v>7.81</v>
+      </c>
+      <c r="Q30" s="30">
+        <v>1.79</v>
+      </c>
+      <c r="R30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>21</v>
       </c>
@@ -1969,43 +2021,43 @@
         <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H31">
-        <v>29.227070000000001</v>
+        <v>29.228750000000002</v>
       </c>
       <c r="I31">
-        <v>83.134839999999997</v>
+        <v>83.135800000000003</v>
       </c>
       <c r="J31" s="30">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="K31">
         <v>5</v>
       </c>
       <c r="L31" s="30">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="M31" s="31">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="N31" s="30">
-        <v>20.260000000000002</v>
+        <v>20.45</v>
       </c>
       <c r="O31" s="30">
-        <v>5.73</v>
+        <v>6.5</v>
       </c>
       <c r="P31" s="30">
-        <v>7.81</v>
+        <v>7.9</v>
       </c>
       <c r="Q31" s="30">
-        <v>1.79</v>
+        <v>0.85</v>
       </c>
       <c r="R31" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>21</v>
       </c>
@@ -2025,43 +2077,43 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H32">
-        <v>29.228750000000002</v>
+        <v>29.233029999999999</v>
       </c>
       <c r="I32">
-        <v>83.135800000000003</v>
+        <v>83.14058</v>
       </c>
       <c r="J32" s="30">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="K32">
         <v>5</v>
       </c>
       <c r="L32" s="30">
+        <v>2</v>
+      </c>
+      <c r="M32" s="31">
+        <v>29.2</v>
+      </c>
+      <c r="N32" s="30">
+        <v>26.7</v>
+      </c>
+      <c r="O32" s="30">
+        <v>6.04</v>
+      </c>
+      <c r="P32" s="30">
+        <v>7.96</v>
+      </c>
+      <c r="Q32" s="30">
         <v>0.75</v>
-      </c>
-      <c r="M32" s="31">
-        <v>28.2</v>
-      </c>
-      <c r="N32" s="30">
-        <v>20.45</v>
-      </c>
-      <c r="O32" s="30">
-        <v>6.5</v>
-      </c>
-      <c r="P32" s="30">
-        <v>7.9</v>
-      </c>
-      <c r="Q32" s="30">
-        <v>0.85</v>
       </c>
       <c r="R32" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>21</v>
       </c>
@@ -2081,43 +2133,43 @@
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33">
-        <v>29.233029999999999</v>
+        <v>29.234159999999999</v>
       </c>
       <c r="I33">
-        <v>83.14058</v>
+        <v>83.142399999999995</v>
       </c>
       <c r="J33" s="30">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="K33">
         <v>5</v>
       </c>
       <c r="L33" s="30">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M33" s="31">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="N33" s="30">
-        <v>26.7</v>
+        <v>20.89</v>
       </c>
       <c r="O33" s="30">
-        <v>6.04</v>
+        <v>6.42</v>
       </c>
       <c r="P33" s="30">
-        <v>7.96</v>
+        <v>7.98</v>
       </c>
       <c r="Q33" s="30">
-        <v>0.75</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>21</v>
       </c>
@@ -2137,43 +2189,43 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>29.234159999999999</v>
+        <v>29.236940000000001</v>
       </c>
       <c r="I34">
-        <v>83.142399999999995</v>
+        <v>83.145399999999995</v>
       </c>
       <c r="J34" s="30">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="K34">
         <v>5</v>
       </c>
       <c r="L34" s="30">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M34" s="31">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="N34" s="30">
-        <v>20.89</v>
+        <v>26.26</v>
       </c>
       <c r="O34" s="30">
-        <v>6.42</v>
+        <v>6.85</v>
       </c>
       <c r="P34" s="30">
-        <v>7.98</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="Q34" s="30">
-        <v>1.9</v>
+        <v>3.24</v>
       </c>
       <c r="R34" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>21</v>
       </c>
@@ -2193,52 +2245,50 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>29.236940000000001</v>
+        <v>29.23076</v>
       </c>
       <c r="I35">
-        <v>83.145399999999995</v>
+        <v>83.137839999999997</v>
       </c>
       <c r="J35" s="30">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="K35">
         <v>5</v>
       </c>
       <c r="L35" s="30">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="M35" s="31">
-        <v>28.9</v>
+        <v>28.5</v>
       </c>
       <c r="N35" s="30">
-        <v>26.26</v>
+        <v>21.96</v>
       </c>
       <c r="O35" s="30">
-        <v>6.85</v>
+        <v>6.7</v>
       </c>
       <c r="P35" s="30">
-        <v>8.0399999999999991</v>
+        <v>7.94</v>
       </c>
       <c r="Q35" s="30">
-        <v>3.24</v>
+        <v>1.26</v>
       </c>
       <c r="R35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="29">
-        <v>45188</v>
-      </c>
+      <c r="C36" s="29"/>
       <c r="D36" t="s">
         <v>23</v>
       </c>
@@ -2246,46 +2296,13 @@
         <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36">
-        <v>29.23076</v>
-      </c>
-      <c r="I36">
-        <v>83.137839999999997</v>
-      </c>
-      <c r="J36" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="K36">
-        <v>5</v>
-      </c>
-      <c r="L36" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="M36" s="31">
-        <v>28.5</v>
-      </c>
-      <c r="N36" s="30">
-        <v>21.96</v>
-      </c>
-      <c r="O36" s="30">
-        <v>6.7</v>
-      </c>
-      <c r="P36" s="30">
-        <v>7.94</v>
-      </c>
-      <c r="Q36" s="30">
-        <v>1.26</v>
-      </c>
-      <c r="R36" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>21</v>
       </c>
@@ -2303,17 +2320,19 @@
         <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="29"/>
+      <c r="C38" s="29">
+        <v>45190</v>
+      </c>
       <c r="D38" t="s">
         <v>23</v>
       </c>
@@ -2324,10 +2343,43 @@
         <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="H38">
+        <v>29.238430000000001</v>
+      </c>
+      <c r="I38">
+        <v>83.077269999999999</v>
+      </c>
+      <c r="J38" s="30">
+        <v>0.35</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+      <c r="L38" s="30">
+        <v>0.35</v>
+      </c>
+      <c r="M38" s="31">
+        <v>27.6</v>
+      </c>
+      <c r="N38" s="30">
+        <v>22.56</v>
+      </c>
+      <c r="O38" s="30">
+        <v>4.46</v>
+      </c>
+      <c r="P38" s="30">
+        <v>7.55</v>
+      </c>
+      <c r="Q38" s="30">
+        <v>6.8</v>
+      </c>
+      <c r="R38" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>21</v>
       </c>
@@ -2347,43 +2399,43 @@
         <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H39">
-        <v>29.238430000000001</v>
+        <v>29.233830000000001</v>
       </c>
       <c r="I39">
-        <v>83.077269999999999</v>
+        <v>83.071669999999997</v>
       </c>
       <c r="J39" s="30">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K39">
         <v>5</v>
       </c>
       <c r="L39" s="30">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="M39" s="31">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="N39" s="30">
-        <v>22.56</v>
+        <v>21.5</v>
       </c>
       <c r="O39" s="30">
-        <v>4.46</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="P39" s="30">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
       <c r="Q39" s="30">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="R39" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>21</v>
       </c>
@@ -2403,52 +2455,49 @@
         <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H40">
-        <v>29.233830000000001</v>
+        <v>29.230920000000001</v>
       </c>
       <c r="I40">
-        <v>83.071669999999997</v>
+        <v>83.076809999999995</v>
       </c>
       <c r="J40" s="30">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K40">
         <v>5</v>
       </c>
       <c r="L40" s="30">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M40" s="31">
-        <v>27.5</v>
+        <v>28.4</v>
       </c>
       <c r="N40" s="30">
-        <v>21.5</v>
+        <v>22.23</v>
       </c>
       <c r="O40" s="30">
-        <v>4.4000000000000004</v>
+        <v>5.22</v>
       </c>
       <c r="P40" s="30">
-        <v>7.56</v>
+        <v>7.66</v>
       </c>
       <c r="Q40" s="30">
-        <v>6.7</v>
+        <v>46.17</v>
       </c>
       <c r="R40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="29">
-        <v>45190</v>
-      </c>
       <c r="D41" t="s">
         <v>23</v>
       </c>
@@ -2459,49 +2508,19 @@
         <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
-      </c>
-      <c r="H41">
-        <v>29.230920000000001</v>
-      </c>
-      <c r="I41">
-        <v>83.076809999999995</v>
-      </c>
-      <c r="J41" s="30">
-        <v>0.3</v>
-      </c>
-      <c r="K41">
-        <v>5</v>
-      </c>
-      <c r="L41" s="30">
-        <v>0.3</v>
-      </c>
-      <c r="M41" s="31">
-        <v>28.4</v>
-      </c>
-      <c r="N41" s="30">
-        <v>22.23</v>
-      </c>
-      <c r="O41" s="30">
-        <v>5.22</v>
-      </c>
-      <c r="P41" s="30">
-        <v>7.66</v>
-      </c>
-      <c r="Q41" s="30">
-        <v>46.17</v>
-      </c>
-      <c r="R41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>76</v>
       </c>
+      <c r="C42" s="29">
+        <v>45187</v>
+      </c>
       <c r="D42" t="s">
         <v>23</v>
       </c>
@@ -2509,13 +2528,46 @@
         <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="H42">
+        <v>29.2639</v>
+      </c>
+      <c r="I42">
+        <v>83.110169999999997</v>
+      </c>
+      <c r="J42" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="M42" s="31">
+        <v>27.5</v>
+      </c>
+      <c r="N42" s="30">
+        <v>0.22</v>
+      </c>
+      <c r="O42" s="30">
+        <v>4.83</v>
+      </c>
+      <c r="P42" s="30">
+        <v>7.38</v>
+      </c>
+      <c r="Q42" s="30">
+        <v>4.3</v>
+      </c>
+      <c r="R42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>21</v>
       </c>
@@ -2535,43 +2587,43 @@
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H43">
-        <v>29.2639</v>
+        <v>29.26548</v>
       </c>
       <c r="I43">
-        <v>83.110169999999997</v>
+        <v>83.117220000000003</v>
       </c>
       <c r="J43" s="30">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43" s="30">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M43" s="31">
-        <v>27.5</v>
+        <v>29.6</v>
       </c>
       <c r="N43" s="30">
-        <v>0.22</v>
+        <v>20.25</v>
       </c>
       <c r="O43" s="30">
-        <v>4.83</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="P43" s="30">
-        <v>7.38</v>
+        <v>7.6</v>
       </c>
       <c r="Q43" s="30">
-        <v>4.3</v>
+        <v>13.6</v>
       </c>
       <c r="R43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>21</v>
       </c>
@@ -2591,43 +2643,43 @@
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H44">
-        <v>29.26548</v>
+        <v>29.263079999999999</v>
       </c>
       <c r="I44">
-        <v>83.117220000000003</v>
+        <v>83.104990000000001</v>
       </c>
       <c r="J44" s="30">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K44">
         <v>5</v>
       </c>
       <c r="L44" s="30">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M44" s="31">
-        <v>29.6</v>
+        <v>27.3</v>
       </c>
       <c r="N44" s="30">
-        <v>20.25</v>
+        <v>0.64</v>
       </c>
       <c r="O44" s="30">
-        <v>4.1399999999999997</v>
+        <v>4.33</v>
       </c>
       <c r="P44" s="30">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="Q44" s="30">
-        <v>13.6</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>21</v>
       </c>
@@ -2647,43 +2699,43 @@
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H45">
-        <v>29.263079999999999</v>
+        <v>29.266850000000002</v>
       </c>
       <c r="I45">
-        <v>83.104990000000001</v>
+        <v>83.108149999999995</v>
       </c>
       <c r="J45" s="30">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K45">
         <v>5</v>
       </c>
       <c r="L45" s="30">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M45" s="31">
-        <v>27.3</v>
+        <v>29.5</v>
       </c>
       <c r="N45" s="30">
-        <v>0.64</v>
+        <v>14.55</v>
       </c>
       <c r="O45" s="30">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="P45" s="30">
-        <v>7.33</v>
+        <v>7.53</v>
       </c>
       <c r="Q45" s="30">
-        <v>8.5299999999999994</v>
+        <v>4.38</v>
       </c>
       <c r="R45" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>21</v>
       </c>
@@ -2703,43 +2755,43 @@
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H46">
-        <v>29.266850000000002</v>
+        <v>29.264140000000001</v>
       </c>
       <c r="I46">
-        <v>83.108149999999995</v>
+        <v>83.112459999999999</v>
       </c>
       <c r="J46" s="30">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="K46">
         <v>5</v>
       </c>
       <c r="L46" s="30">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M46" s="31">
-        <v>29.5</v>
+        <v>28.6</v>
       </c>
       <c r="N46" s="30">
-        <v>14.55</v>
+        <v>11.64</v>
       </c>
       <c r="O46" s="30">
-        <v>4.57</v>
+        <v>3.85</v>
       </c>
       <c r="P46" s="30">
-        <v>7.53</v>
+        <v>7.37</v>
       </c>
       <c r="Q46" s="30">
-        <v>4.38</v>
+        <v>8.83</v>
       </c>
       <c r="R46" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>21</v>
       </c>
@@ -2759,51 +2811,49 @@
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47">
-        <v>29.264140000000001</v>
+        <v>29.268989999999999</v>
       </c>
       <c r="I47">
-        <v>83.112459999999999</v>
+        <v>83.112350000000006</v>
       </c>
       <c r="J47" s="30">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="K47">
         <v>5</v>
       </c>
       <c r="L47" s="30">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="M47" s="31">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="N47" s="30">
-        <v>11.64</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="O47" s="30">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="P47" s="30">
-        <v>7.37</v>
+        <v>7.49</v>
       </c>
       <c r="Q47" s="30">
-        <v>8.83</v>
+        <v>3.98</v>
       </c>
       <c r="R47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B48" s="17"/>
       <c r="C48" s="29">
-        <v>45187</v>
+        <v>45250</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -2812,46 +2862,46 @@
         <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H48">
-        <v>29.268989999999999</v>
+        <v>29.226649999999999</v>
       </c>
       <c r="I48">
-        <v>83.112350000000006</v>
+        <v>83.135419999999996</v>
       </c>
       <c r="J48" s="30">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L48" s="30">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="M48" s="31">
-        <v>29.4</v>
+        <v>20.8</v>
       </c>
       <c r="N48" s="30">
-        <v>18.850000000000001</v>
+        <v>24.61</v>
       </c>
       <c r="O48" s="30">
-        <v>3.44</v>
+        <v>7.64</v>
       </c>
       <c r="P48" s="30">
-        <v>7.49</v>
+        <v>7.95</v>
       </c>
       <c r="Q48" s="30">
-        <v>3.98</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="R48" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>22</v>
       </c>
@@ -2869,13 +2919,13 @@
         <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H49">
-        <v>29.226649999999999</v>
+        <v>29.22897</v>
       </c>
       <c r="I49">
-        <v>83.135419999999996</v>
+        <v>83.135999999999996</v>
       </c>
       <c r="J49" s="30">
         <v>1.25</v>
@@ -2887,25 +2937,25 @@
         <v>1.25</v>
       </c>
       <c r="M49" s="31">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N49" s="30">
-        <v>24.61</v>
+        <v>28.36</v>
       </c>
       <c r="O49" s="30">
-        <v>7.64</v>
+        <v>6.93</v>
       </c>
       <c r="P49" s="30">
-        <v>7.95</v>
+        <v>7.96</v>
       </c>
       <c r="Q49" s="30">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="R49" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>22</v>
       </c>
@@ -2923,43 +2973,43 @@
         <v>27</v>
       </c>
       <c r="G50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H50">
-        <v>29.22897</v>
+        <v>29.233239999999999</v>
       </c>
       <c r="I50">
-        <v>83.135999999999996</v>
+        <v>83.141279999999995</v>
       </c>
       <c r="J50" s="30">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="K50">
         <v>15</v>
       </c>
       <c r="L50" s="30">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="M50" s="31">
         <v>21.1</v>
       </c>
       <c r="N50" s="30">
-        <v>28.36</v>
+        <v>29.53</v>
       </c>
       <c r="O50" s="30">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="P50" s="30">
-        <v>7.96</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="Q50" s="30">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="R50" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>22</v>
       </c>
@@ -2977,31 +3027,31 @@
         <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51">
-        <v>29.233239999999999</v>
+        <v>29.234120000000001</v>
       </c>
       <c r="I51">
-        <v>83.141279999999995</v>
+        <v>83.14273</v>
       </c>
       <c r="J51" s="30">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K51">
         <v>15</v>
       </c>
       <c r="L51" s="30">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M51" s="31">
         <v>21.1</v>
       </c>
       <c r="N51" s="30">
-        <v>29.53</v>
+        <v>30.3</v>
       </c>
       <c r="O51" s="30">
-        <v>7.07</v>
+        <v>7.02</v>
       </c>
       <c r="P51" s="30">
         <v>8.0299999999999994</v>
@@ -3013,11 +3063,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B52" s="17"/>
       <c r="C52" s="29">
         <v>45250</v>
       </c>
@@ -3031,43 +3080,43 @@
         <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H52">
-        <v>29.234120000000001</v>
+        <v>29.236249999999998</v>
       </c>
       <c r="I52">
-        <v>83.14273</v>
+        <v>83.145560000000003</v>
       </c>
       <c r="J52" s="30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="K52">
         <v>15</v>
       </c>
       <c r="L52" s="30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M52" s="31">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="N52" s="30">
-        <v>30.3</v>
+        <v>29.72</v>
       </c>
       <c r="O52" s="30">
-        <v>7.02</v>
+        <v>7.15</v>
       </c>
       <c r="P52" s="30">
-        <v>8.0299999999999994</v>
+        <v>8.02</v>
       </c>
       <c r="Q52" s="30">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="R52" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>22</v>
       </c>
@@ -3084,48 +3133,48 @@
         <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H53">
-        <v>29.236249999999998</v>
+        <v>29.23104</v>
       </c>
       <c r="I53">
-        <v>83.145560000000003</v>
+        <v>83.138559999999998</v>
       </c>
       <c r="J53" s="30">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="K53">
         <v>15</v>
       </c>
       <c r="L53" s="30">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="M53" s="31">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="N53" s="30">
-        <v>29.72</v>
+        <v>30.87</v>
       </c>
       <c r="O53" s="30">
-        <v>7.15</v>
+        <v>7.08</v>
       </c>
       <c r="P53" s="30">
-        <v>8.02</v>
+        <v>8.01</v>
       </c>
       <c r="Q53" s="30">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="R53" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C54" s="29">
-        <v>45250</v>
+        <v>45309</v>
       </c>
       <c r="D54" t="s">
         <v>23</v>
@@ -3134,46 +3183,46 @@
         <v>24</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H54">
-        <v>29.23104</v>
+        <v>29.238710000000001</v>
       </c>
       <c r="I54">
-        <v>83.138559999999998</v>
+        <v>83.07056</v>
       </c>
       <c r="J54" s="30">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="K54">
         <v>15</v>
       </c>
       <c r="L54" s="30">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M54" s="31">
-        <v>20.9</v>
+        <v>10.4</v>
       </c>
       <c r="N54" s="30">
-        <v>30.87</v>
+        <v>11.89</v>
       </c>
       <c r="O54" s="30">
-        <v>7.08</v>
+        <v>9.85</v>
       </c>
       <c r="P54" s="30">
-        <v>8.01</v>
+        <v>7.81</v>
       </c>
       <c r="Q54" s="30">
-        <v>0.18</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="R54" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
         <v>22</v>
       </c>
@@ -3190,43 +3239,43 @@
         <v>28</v>
       </c>
       <c r="G55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55">
-        <v>29.238710000000001</v>
+        <v>29.239419999999999</v>
       </c>
       <c r="I55">
-        <v>83.07056</v>
+        <v>83.072890000000001</v>
       </c>
       <c r="J55" s="30">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K55">
         <v>15</v>
       </c>
       <c r="L55" s="30">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M55" s="31">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="N55" s="30">
-        <v>11.89</v>
+        <v>11.65</v>
       </c>
       <c r="O55" s="30">
-        <v>9.85</v>
+        <v>10.27</v>
       </c>
       <c r="P55" s="30">
-        <v>7.81</v>
+        <v>7.87</v>
       </c>
       <c r="Q55" s="30">
-        <v>20.420000000000002</v>
+        <v>24.31</v>
       </c>
       <c r="R55" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
         <v>22</v>
       </c>
@@ -3243,13 +3292,13 @@
         <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H56">
-        <v>29.239419999999999</v>
+        <v>29.23847</v>
       </c>
       <c r="I56">
-        <v>83.072890000000001</v>
+        <v>83.077449999999999</v>
       </c>
       <c r="J56" s="30">
         <v>0.5</v>
@@ -3261,25 +3310,25 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="31">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="N56" s="30">
-        <v>11.65</v>
+        <v>11.11</v>
       </c>
       <c r="O56" s="30">
-        <v>10.27</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="P56" s="30">
-        <v>7.87</v>
+        <v>7.79</v>
       </c>
       <c r="Q56" s="30">
-        <v>24.31</v>
+        <v>7.3</v>
       </c>
       <c r="R56" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>22</v>
       </c>
@@ -3296,13 +3345,13 @@
         <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H57">
-        <v>29.23847</v>
+        <v>29.233979999999999</v>
       </c>
       <c r="I57">
-        <v>83.077449999999999</v>
+        <v>83.071969999999993</v>
       </c>
       <c r="J57" s="30">
         <v>0.5</v>
@@ -3314,25 +3363,25 @@
         <v>0.5</v>
       </c>
       <c r="M57" s="31">
-        <v>10.7</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="N57" s="30">
-        <v>11.11</v>
+        <v>14.33</v>
       </c>
       <c r="O57" s="30">
-        <v>9.9700000000000006</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="P57" s="30">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="Q57" s="30">
-        <v>7.3</v>
+        <v>7.61</v>
       </c>
       <c r="R57" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
         <v>22</v>
       </c>
@@ -3349,43 +3398,43 @@
         <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H58">
-        <v>29.233979999999999</v>
+        <v>29.230899999999998</v>
       </c>
       <c r="I58">
-        <v>83.071969999999993</v>
+        <v>83.077119999999994</v>
       </c>
       <c r="J58" s="30">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K58">
         <v>15</v>
       </c>
       <c r="L58" s="30">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="M58" s="31">
-        <v>10.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="N58" s="30">
-        <v>14.33</v>
+        <v>11.99</v>
       </c>
       <c r="O58" s="30">
-        <v>9.3699999999999992</v>
+        <v>9.85</v>
       </c>
       <c r="P58" s="30">
-        <v>7.76</v>
+        <v>7.81</v>
       </c>
       <c r="Q58" s="30">
-        <v>7.61</v>
+        <v>13.83</v>
       </c>
       <c r="R58" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
         <v>22</v>
       </c>
@@ -3402,48 +3451,48 @@
         <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H59">
-        <v>29.230899999999998</v>
+        <v>29.235849999999999</v>
       </c>
       <c r="I59">
-        <v>83.077119999999994</v>
+        <v>83.072320000000005</v>
       </c>
       <c r="J59" s="30">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K59">
         <v>15</v>
       </c>
       <c r="L59" s="30">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M59" s="31">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="N59" s="30">
-        <v>11.99</v>
+        <v>12.61</v>
       </c>
       <c r="O59" s="30">
-        <v>9.85</v>
+        <v>9.69</v>
       </c>
       <c r="P59" s="30">
-        <v>7.81</v>
+        <v>7.79</v>
       </c>
       <c r="Q59" s="30">
-        <v>13.83</v>
+        <v>6.23</v>
       </c>
       <c r="R59" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C60" s="29">
-        <v>45309</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="s">
         <v>23</v>
@@ -3452,46 +3501,46 @@
         <v>24</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H60">
-        <v>29.235849999999999</v>
+        <v>29.264150000000001</v>
       </c>
       <c r="I60">
-        <v>83.072320000000005</v>
+        <v>83.110860000000002</v>
       </c>
       <c r="J60" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>15</v>
       </c>
       <c r="L60" s="30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M60" s="31">
-        <v>10.3</v>
+        <v>18.8</v>
       </c>
       <c r="N60" s="30">
-        <v>12.61</v>
+        <v>22.95</v>
       </c>
       <c r="O60" s="30">
-        <v>9.69</v>
+        <v>7.48</v>
       </c>
       <c r="P60" s="30">
-        <v>7.79</v>
+        <v>7.88</v>
       </c>
       <c r="Q60" s="30">
-        <v>6.23</v>
+        <v>0.78</v>
       </c>
       <c r="R60" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>22</v>
       </c>
@@ -3508,43 +3557,43 @@
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H61">
-        <v>29.264150000000001</v>
+        <v>29.265940000000001</v>
       </c>
       <c r="I61">
-        <v>83.110860000000002</v>
+        <v>83.117040000000003</v>
       </c>
       <c r="J61" s="30">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K61">
         <v>15</v>
       </c>
       <c r="L61" s="30">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M61" s="31">
-        <v>18.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="N61" s="30">
-        <v>22.95</v>
+        <v>10.88</v>
       </c>
       <c r="O61" s="30">
-        <v>7.48</v>
+        <v>7.23</v>
       </c>
       <c r="P61" s="30">
-        <v>7.88</v>
+        <v>7.76</v>
       </c>
       <c r="Q61" s="30">
-        <v>0.78</v>
+        <v>0.49</v>
       </c>
       <c r="R61" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="s">
         <v>22</v>
       </c>
@@ -3561,43 +3610,43 @@
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H62">
-        <v>29.265940000000001</v>
+        <v>29.262840000000001</v>
       </c>
       <c r="I62">
-        <v>83.117040000000003</v>
+        <v>83.104680000000002</v>
       </c>
       <c r="J62" s="30">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K62">
         <v>15</v>
       </c>
       <c r="L62" s="30">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M62" s="31">
-        <v>18.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="N62" s="30">
-        <v>10.88</v>
+        <v>22.83</v>
       </c>
       <c r="O62" s="30">
-        <v>7.23</v>
+        <v>7.68</v>
       </c>
       <c r="P62" s="30">
-        <v>7.76</v>
+        <v>7.96</v>
       </c>
       <c r="Q62" s="30">
-        <v>0.49</v>
+        <v>11.22</v>
       </c>
       <c r="R62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>22</v>
       </c>
@@ -3614,43 +3663,43 @@
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H63">
-        <v>29.262840000000001</v>
+        <v>29.267430000000001</v>
       </c>
       <c r="I63">
-        <v>83.104680000000002</v>
+        <v>83.106870000000001</v>
       </c>
       <c r="J63" s="30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K63">
         <v>15</v>
       </c>
       <c r="L63" s="30">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M63" s="31">
-        <v>19</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="N63" s="30">
-        <v>22.83</v>
+        <v>10.79</v>
       </c>
       <c r="O63" s="30">
-        <v>7.68</v>
+        <v>6.98</v>
       </c>
       <c r="P63" s="30">
-        <v>7.96</v>
+        <v>7.72</v>
       </c>
       <c r="Q63" s="30">
-        <v>11.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="R63" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>22</v>
       </c>
@@ -3667,43 +3716,43 @@
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H64">
-        <v>29.267430000000001</v>
+        <v>29.26398</v>
       </c>
       <c r="I64">
-        <v>83.106870000000001</v>
+        <v>83.112520000000004</v>
       </c>
       <c r="J64" s="30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="K64">
         <v>15</v>
       </c>
       <c r="L64" s="30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M64" s="31">
-        <v>19.100000000000001</v>
+        <v>18.7</v>
       </c>
       <c r="N64" s="30">
-        <v>10.79</v>
+        <v>19.45</v>
       </c>
       <c r="O64" s="30">
-        <v>6.98</v>
+        <v>6.84</v>
       </c>
       <c r="P64" s="30">
-        <v>7.72</v>
+        <v>7.86</v>
       </c>
       <c r="Q64" s="30">
-        <v>0.14000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="R64" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>22</v>
       </c>
@@ -3720,48 +3769,49 @@
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65">
-        <v>29.26398</v>
+        <v>29.268930000000001</v>
       </c>
       <c r="I65">
-        <v>83.112520000000004</v>
+        <v>83.112449999999995</v>
       </c>
       <c r="J65" s="30">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="K65">
         <v>15</v>
       </c>
       <c r="L65" s="30">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="M65" s="31">
-        <v>18.7</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="N65" s="30">
-        <v>19.45</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="O65" s="30">
-        <v>6.84</v>
+        <v>7.12</v>
       </c>
       <c r="P65" s="30">
-        <v>7.86</v>
+        <v>7.7</v>
       </c>
       <c r="Q65" s="30">
-        <v>0.46</v>
+        <v>0.1</v>
       </c>
       <c r="R65" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>22</v>
       </c>
+      <c r="B66" s="17"/>
       <c r="C66" s="29">
-        <v>45264</v>
+        <v>45315</v>
       </c>
       <c r="D66" t="s">
         <v>23</v>
@@ -3773,49 +3823,49 @@
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H66">
-        <v>29.268930000000001</v>
+        <v>29.267469999999999</v>
       </c>
       <c r="I66">
-        <v>83.112449999999995</v>
+        <v>83.082440000000005</v>
       </c>
       <c r="J66" s="30">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K66">
         <v>15</v>
       </c>
       <c r="L66" s="30">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M66" s="31">
-        <v>19.100000000000001</v>
+        <v>14</v>
       </c>
       <c r="N66" s="30">
-        <v>4.3499999999999996</v>
+        <v>9.4</v>
       </c>
       <c r="O66" s="30">
-        <v>7.12</v>
+        <v>7.84</v>
       </c>
       <c r="P66" s="30">
-        <v>7.7</v>
+        <v>7.49</v>
       </c>
       <c r="Q66" s="30">
-        <v>0.1</v>
+        <v>12.2</v>
       </c>
       <c r="R66" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="29">
-        <v>45315</v>
+        <v>45317</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
@@ -3827,49 +3877,49 @@
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H67">
-        <v>29.267469999999999</v>
+        <v>29.25881</v>
       </c>
       <c r="I67">
-        <v>83.082440000000005</v>
+        <v>83.07611</v>
       </c>
       <c r="J67" s="30">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K67">
         <v>15</v>
       </c>
       <c r="L67" s="30">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M67" s="31">
-        <v>14</v>
+        <v>20.5</v>
       </c>
       <c r="N67" s="30">
-        <v>9.4</v>
+        <v>13.93</v>
       </c>
       <c r="O67" s="30">
-        <v>7.84</v>
+        <v>6.48</v>
       </c>
       <c r="P67" s="30">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
       <c r="Q67" s="30">
-        <v>12.2</v>
+        <v>7.56</v>
       </c>
       <c r="R67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="29">
-        <v>45317</v>
+        <v>45315</v>
       </c>
       <c r="D68" t="s">
         <v>23</v>
@@ -3881,43 +3931,43 @@
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H68">
-        <v>29.25881</v>
+        <v>29.264230000000001</v>
       </c>
       <c r="I68">
-        <v>83.07611</v>
+        <v>83.080609999999993</v>
       </c>
       <c r="J68" s="30">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K68">
         <v>15</v>
       </c>
       <c r="L68" s="30">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M68" s="31">
-        <v>20.5</v>
+        <v>15.9</v>
       </c>
       <c r="N68" s="30">
-        <v>13.93</v>
+        <v>17.62</v>
       </c>
       <c r="O68" s="30">
-        <v>6.48</v>
+        <v>9.73</v>
       </c>
       <c r="P68" s="30">
-        <v>7.46</v>
+        <v>7.87</v>
       </c>
       <c r="Q68" s="30">
-        <v>7.56</v>
+        <v>10.77</v>
       </c>
       <c r="R68" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>22</v>
       </c>
@@ -3935,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H69">
-        <v>29.264230000000001</v>
+        <v>29.265809999999998</v>
       </c>
       <c r="I69">
-        <v>83.080609999999993</v>
+        <v>83.081019999999995</v>
       </c>
       <c r="J69" s="30">
         <v>0.5</v>
@@ -3953,31 +4003,31 @@
         <v>0.5</v>
       </c>
       <c r="M69" s="31">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
       <c r="N69" s="30">
-        <v>17.62</v>
+        <v>15.82</v>
       </c>
       <c r="O69" s="30">
-        <v>9.73</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="P69" s="30">
-        <v>7.87</v>
+        <v>7.74</v>
       </c>
       <c r="Q69" s="30">
-        <v>10.77</v>
+        <v>6.54</v>
       </c>
       <c r="R69" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="29">
-        <v>45315</v>
+        <v>45317</v>
       </c>
       <c r="D70" t="s">
         <v>23</v>
@@ -3989,13 +4039,13 @@
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H70">
-        <v>29.265809999999998</v>
+        <v>29.26051</v>
       </c>
       <c r="I70">
-        <v>83.081019999999995</v>
+        <v>83.070049999999995</v>
       </c>
       <c r="J70" s="30">
         <v>0.5</v>
@@ -4007,25 +4057,25 @@
         <v>0.5</v>
       </c>
       <c r="M70" s="31">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="N70" s="30">
-        <v>15.82</v>
+        <v>13.24</v>
       </c>
       <c r="O70" s="30">
-        <v>8.9700000000000006</v>
+        <v>7.24</v>
       </c>
       <c r="P70" s="30">
-        <v>7.74</v>
+        <v>7.57</v>
       </c>
       <c r="Q70" s="30">
-        <v>6.54</v>
+        <v>7.28</v>
       </c>
       <c r="R70" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>22</v>
       </c>
@@ -4043,13 +4093,13 @@
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H71">
-        <v>29.26051</v>
+        <v>29.260850000000001</v>
       </c>
       <c r="I71">
-        <v>83.070049999999995</v>
+        <v>83.073989999999995</v>
       </c>
       <c r="J71" s="30">
         <v>0.5</v>
@@ -4061,80 +4111,26 @@
         <v>0.5</v>
       </c>
       <c r="M71" s="31">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N71" s="30">
-        <v>13.24</v>
+        <v>13.41</v>
       </c>
       <c r="O71" s="30">
-        <v>7.24</v>
+        <v>6.27</v>
       </c>
       <c r="P71" s="30">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="Q71" s="30">
-        <v>7.28</v>
+        <v>10.48</v>
       </c>
       <c r="R71" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="29">
-        <v>45317</v>
-      </c>
-      <c r="D72" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" t="s">
-        <v>53</v>
-      </c>
-      <c r="H72">
-        <v>29.260850000000001</v>
-      </c>
-      <c r="I72">
-        <v>83.073989999999995</v>
-      </c>
-      <c r="J72" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="K72">
-        <v>15</v>
-      </c>
-      <c r="L72" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="M72" s="31">
-        <v>20.7</v>
-      </c>
-      <c r="N72" s="30">
-        <v>13.41</v>
-      </c>
-      <c r="O72" s="30">
-        <v>6.27</v>
-      </c>
-      <c r="P72" s="30">
-        <v>7.45</v>
-      </c>
-      <c r="Q72" s="30">
-        <v>10.48</v>
-      </c>
-      <c r="R72" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="S73" s="32" t="s">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S72" s="32" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4144,240 +4140,348 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="28">
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C2DCDA6-8762-4F8E-BE10-342A96D81F01}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="40">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1FC68605-CB70-461B-A1CA-DF1EDFF4B328}">
           <x14:formula1>
             <xm:f>Notes!D56</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>Notes!E56</xm:f>
           </x14:formula2>
-          <xm:sqref>L49:L54 J49:J1048574</xm:sqref>
+          <xm:sqref>L48:L53 J48:J1048573</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{97D0CF3F-1331-4992-952C-2CD737F9EF05}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{461A564B-1FC7-43EC-B968-F2C806BFC7EA}">
           <x14:formula1>
             <xm:f>Notes!D14</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>Notes!E14</xm:f>
           </x14:formula2>
-          <xm:sqref>L55:L1048576 L6:L48</xm:sqref>
+          <xm:sqref>L54:L1048576 L6:L29</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C689F7BD-0785-484E-A5B7-3243AC2CEE36}">
+        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A1355FA-D27F-4B8B-A07B-E4C8A2B1EEFE}">
+          <x14:formula1>
+            <xm:f>Notes!D25</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E25</xm:f>
+          </x14:formula2>
+          <xm:sqref>C30:C37</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{381178A4-B3EB-42BA-85FC-D77FD7D54957}">
+          <x14:formula1>
+            <xm:f>Notes!D13</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E13</xm:f>
+          </x14:formula2>
+          <xm:sqref>C1048574:C1048576 C14:C29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{381538AD-438D-46F2-A9E1-7EEE7A3E6A6B}">
+          <x14:formula1>
+            <xm:f>Notes!D49</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E49</xm:f>
+          </x14:formula2>
+          <xm:sqref>C48:C1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{722A62A4-6DF9-420D-9305-62F49471BC1B}">
+          <x14:formula1>
+            <xm:f>Notes!D10</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E10</xm:f>
+          </x14:formula2>
+          <xm:sqref>H1048574:H1048576 H6:H29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E8B297C-A5B0-4522-867D-1F495CFA0FDF}">
+          <x14:formula1>
+            <xm:f>Notes!D54</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E54</xm:f>
+          </x14:formula2>
+          <xm:sqref>H48:H1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{74BBBC44-309C-4A0B-8F07-7AC1C492D49E}">
+          <x14:formula1>
+            <xm:f>Notes!D11</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E11</xm:f>
+          </x14:formula2>
+          <xm:sqref>I1048574:I1048576 I6:I29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72B8AFD8-F344-4903-9AF4-3979A5EEBF81}">
+          <x14:formula1>
+            <xm:f>Notes!D55</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E55</xm:f>
+          </x14:formula2>
+          <xm:sqref>I48:I1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7D780899-DDFD-4D2E-8552-DE103A3570D4}">
+          <x14:formula1>
+            <xm:f>Notes!D12</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E12</xm:f>
+          </x14:formula2>
+          <xm:sqref>J1048574:J1048576 J6:J29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B1B8919E-4E39-48C5-B02D-76D8C3975865}">
+          <x14:formula1>
+            <xm:f>Notes!D13</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E13</xm:f>
+          </x14:formula2>
+          <xm:sqref>K1048574:K1048576 K6:K29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B10BF8DC-0336-4230-92D1-5AF90438F610}">
+          <x14:formula1>
+            <xm:f>Notes!D57</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E57</xm:f>
+          </x14:formula2>
+          <xm:sqref>K48:K1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{97920D18-7588-41FF-813A-61B2677FE7A9}">
+          <x14:formula1>
+            <xm:f>Notes!D15</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E15</xm:f>
+          </x14:formula2>
+          <xm:sqref>M1048574:M1048576 M6:M29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A381E0A9-EBB2-4FED-B08A-4ABA215F6B61}">
+          <x14:formula1>
+            <xm:f>Notes!D59</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E59</xm:f>
+          </x14:formula2>
+          <xm:sqref>M48:M1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BF83226B-73E4-4076-A45B-3ECBD30CC850}">
+          <x14:formula1>
+            <xm:f>Notes!D16</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E16</xm:f>
+          </x14:formula2>
+          <xm:sqref>N1048574:N1048576 N6:N29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{970095AF-F79C-4574-9011-290AAE21A60E}">
+          <x14:formula1>
+            <xm:f>Notes!D60</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E60</xm:f>
+          </x14:formula2>
+          <xm:sqref>N48:N1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6A26B449-7AF1-4635-B2D7-791DC2A86548}">
+          <x14:formula1>
+            <xm:f>Notes!D17</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E17</xm:f>
+          </x14:formula2>
+          <xm:sqref>O1048574:O1048576 O6:O29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{031D3A29-DB5E-48A1-97B5-591703C33210}">
+          <x14:formula1>
+            <xm:f>Notes!D61</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E61</xm:f>
+          </x14:formula2>
+          <xm:sqref>O48:O1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D034164D-4C4E-41D8-AEBE-53E073AA9C9F}">
+          <x14:formula1>
+            <xm:f>Notes!D18</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E18</xm:f>
+          </x14:formula2>
+          <xm:sqref>P1048574:P1048576 P6:P29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9699AD59-2F7A-4592-91EB-44D7C34F4B9D}">
+          <x14:formula1>
+            <xm:f>Notes!D62</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E62</xm:f>
+          </x14:formula2>
+          <xm:sqref>P48:P1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{220F69D4-1E9E-46BE-923E-AF3AD89AC4CB}">
+          <x14:formula1>
+            <xm:f>Notes!D19</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E19</xm:f>
+          </x14:formula2>
+          <xm:sqref>Q1048574:Q1048576 Q6:Q29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87647AAA-11D4-4FED-BDFC-EA84D02D069D}">
+          <x14:formula1>
+            <xm:f>Notes!D63</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E63</xm:f>
+          </x14:formula2>
+          <xm:sqref>Q48:Q1048573</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9D2C1238-2F1C-4176-B7B4-4C67BF8FFE63}">
+          <x14:formula1>
+            <xm:f>Notes!D39</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Notes!E39</xm:f>
+          </x14:formula2>
+          <xm:sqref>L30:L47</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07C0DC6C-6B50-44D7-9A16-463F2EC65446}">
           <x14:formula1>
             <xm:f>Notes!$C$2:$D$2</xm:f>
           </x14:formula1>
           <xm:sqref>A6:A1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E8805226-D9C1-4394-B1C2-8A349A4FC218}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C5B1748E-C7F0-4D51-B12B-0351CB018F81}">
           <x14:formula1>
             <xm:f>Notes!$C$5</xm:f>
           </x14:formula1>
           <xm:sqref>D6:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1DCBAB76-F7A2-47D5-A0CE-71FDFB81498A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A1EC685E-1E25-4F33-BBF5-94ADEB5DE47E}">
           <x14:formula1>
             <xm:f>Notes!$C$6</xm:f>
           </x14:formula1>
           <xm:sqref>E6:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{98489461-A119-46CC-AF25-679062C6BBCE}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{585CA8F3-0AAA-474B-A005-476DE2972C33}">
           <x14:formula1>
             <xm:f>Notes!$C$7:$E$7</xm:f>
           </x14:formula1>
           <xm:sqref>F6:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{251A844F-96C0-4AE6-B6D3-7651898556CF}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B6BE02A-8758-4576-B547-9EB65C07AA77}">
           <x14:formula1>
             <xm:f>Notes!$C$9:$Z$9</xm:f>
           </x14:formula1>
           <xm:sqref>G6:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3FB15AF-45A9-40FB-9125-163DCBF725B6}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{64E13D37-A91E-4C9F-B0A7-AD27C1B2038A}">
           <x14:formula1>
             <xm:f>Notes!$C$3:$E$3</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D7FC2CD6-E74C-4BD2-A012-C4D05D597F37}">
+        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E8BA6AE0-267D-4C1C-AB32-A8FCA3EE20F0}">
           <x14:formula1>
             <xm:f>Notes!D1048576</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>Notes!E1048576</xm:f>
           </x14:formula2>
-          <xm:sqref>C6:C13 C31:C38</xm:sqref>
+          <xm:sqref>C6:C13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA579B7C-373B-45CB-9755-1780A980D5AF}">
+        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CF14BAEC-AC71-4BC2-9E37-61BD76C55DE5}">
           <x14:formula1>
-            <xm:f>Notes!D13</xm:f>
+            <xm:f>Notes!D38</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E13</xm:f>
+            <xm:f>Notes!E38</xm:f>
           </x14:formula2>
-          <xm:sqref>C14:C30 C1048575:C1048576 C39:C48</xm:sqref>
+          <xm:sqref>C38:C47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2FF2BE1-2D3E-4E57-A57C-7FCEE63468F3}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7AE3711D-720E-4166-B0FE-9DDD1045B591}">
           <x14:formula1>
-            <xm:f>Notes!D49</xm:f>
+            <xm:f>Notes!D35</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E49</xm:f>
+            <xm:f>Notes!E35</xm:f>
           </x14:formula2>
-          <xm:sqref>C49:C1048574</xm:sqref>
+          <xm:sqref>H30:H47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CFC4F2E-F063-409F-BE00-508D03F9659E}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E8B0FD0-307B-4BEC-B37A-1291A198CB8A}">
           <x14:formula1>
-            <xm:f>Notes!D10</xm:f>
+            <xm:f>Notes!D36</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E10</xm:f>
+            <xm:f>Notes!E36</xm:f>
           </x14:formula2>
-          <xm:sqref>H6:H48 H1048575:H1048576</xm:sqref>
+          <xm:sqref>I30:I47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BB81E5BC-16A5-42B3-8733-870BA9A0CD14}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8C6031CF-E153-4FEE-A10C-7652A83021AB}">
           <x14:formula1>
-            <xm:f>Notes!D54</xm:f>
+            <xm:f>Notes!D37</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E54</xm:f>
+            <xm:f>Notes!E37</xm:f>
           </x14:formula2>
-          <xm:sqref>H49:H1048574</xm:sqref>
+          <xm:sqref>J30:J47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{222DE298-32EB-472C-9A91-2961D747A923}">
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EA4406F-D5E5-4F14-A08E-28FAD8E3F0AB}">
           <x14:formula1>
-            <xm:f>Notes!D11</xm:f>
+            <xm:f>Notes!D38</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E11</xm:f>
+            <xm:f>Notes!E38</xm:f>
           </x14:formula2>
-          <xm:sqref>I6:I48 I1048575:I1048576</xm:sqref>
+          <xm:sqref>K30:K47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{081473C5-6DC2-4475-8537-58A773295C24}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{139E88D4-B6D3-482E-BA38-D42D170E2D8D}">
           <x14:formula1>
-            <xm:f>Notes!D55</xm:f>
+            <xm:f>Notes!D40</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E55</xm:f>
+            <xm:f>Notes!E40</xm:f>
           </x14:formula2>
-          <xm:sqref>I49:I1048574</xm:sqref>
+          <xm:sqref>M30:M47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA605E6B-2AC2-43DB-8BA3-7E27279DBAE7}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE450C97-065E-41F3-A1F0-2286EACA6033}">
           <x14:formula1>
-            <xm:f>Notes!D12</xm:f>
+            <xm:f>Notes!D41</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E12</xm:f>
+            <xm:f>Notes!E41</xm:f>
           </x14:formula2>
-          <xm:sqref>J6:J48 J1048575:J1048576</xm:sqref>
+          <xm:sqref>N30:N47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{367176EA-37D2-43DC-B418-0063BF222420}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{912B97DA-BBF2-4BF3-B617-888E186196FE}">
           <x14:formula1>
-            <xm:f>Notes!D13</xm:f>
+            <xm:f>Notes!D42</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E13</xm:f>
+            <xm:f>Notes!E42</xm:f>
           </x14:formula2>
-          <xm:sqref>K6:K48 K1048575:K1048576</xm:sqref>
+          <xm:sqref>O30:O47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{88E794DF-0D02-4312-B11F-769A3CE675E3}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B58D9F7C-0A56-4273-A83D-43DE276F7935}">
           <x14:formula1>
-            <xm:f>Notes!D57</xm:f>
+            <xm:f>Notes!D43</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E57</xm:f>
+            <xm:f>Notes!E43</xm:f>
           </x14:formula2>
-          <xm:sqref>K49:K1048574</xm:sqref>
+          <xm:sqref>P30:P47</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B1ED8242-4ECE-40ED-988D-55EC75071994}">
+        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3FF32E2B-66CF-41B2-AD6C-8D163B5F4B20}">
           <x14:formula1>
-            <xm:f>Notes!D15</xm:f>
+            <xm:f>Notes!D44</xm:f>
           </x14:formula1>
           <x14:formula2>
-            <xm:f>Notes!E15</xm:f>
+            <xm:f>Notes!E44</xm:f>
           </x14:formula2>
-          <xm:sqref>M6:M48 M1048575:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AF85B792-7586-4BFE-A846-5AF4D0A28939}">
-          <x14:formula1>
-            <xm:f>Notes!D59</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E59</xm:f>
-          </x14:formula2>
-          <xm:sqref>M49:M1048574</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE1A1CA6-3E24-4B32-B710-602ABAE1208D}">
-          <x14:formula1>
-            <xm:f>Notes!D16</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E16</xm:f>
-          </x14:formula2>
-          <xm:sqref>N6:N48 N1048575:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FC865CD9-6E8C-4E0D-B3B0-B29553B8D672}">
-          <x14:formula1>
-            <xm:f>Notes!D60</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E60</xm:f>
-          </x14:formula2>
-          <xm:sqref>N49:N1048574</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6207B3E7-6D5D-4292-89F9-3E1241828991}">
-          <x14:formula1>
-            <xm:f>Notes!D17</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E17</xm:f>
-          </x14:formula2>
-          <xm:sqref>O6:O48 O1048575:O1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{60F1D455-4F75-4AD6-BE78-945EE4239D16}">
-          <x14:formula1>
-            <xm:f>Notes!D61</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E61</xm:f>
-          </x14:formula2>
-          <xm:sqref>O49:O1048574</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72342D57-40D0-409E-886E-82E8A1BD1907}">
-          <x14:formula1>
-            <xm:f>Notes!D18</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E18</xm:f>
-          </x14:formula2>
-          <xm:sqref>P6:P48 P1048575:P1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5F8155E1-CD28-4BFD-A829-0695710DA8E1}">
-          <x14:formula1>
-            <xm:f>Notes!D62</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E62</xm:f>
-          </x14:formula2>
-          <xm:sqref>P49:P1048574</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7370A1C8-23FD-4D5D-AA4F-0B26D5E6EFF6}">
-          <x14:formula1>
-            <xm:f>Notes!D19</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E19</xm:f>
-          </x14:formula2>
-          <xm:sqref>Q6:Q48 Q1048575:Q1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9839E8E7-3D44-41A6-A9A3-D286F1098D46}">
-          <x14:formula1>
-            <xm:f>Notes!D63</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Notes!E63</xm:f>
-          </x14:formula2>
-          <xm:sqref>Q49:Q1048574</xm:sqref>
+          <xm:sqref>Q30:Q47</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4388,15 +4492,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC46B2A7-99E3-4251-99D9-CE71B307265A}">
   <dimension ref="A1:Z47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>18</v>
       </c>
@@ -4413,7 +4517,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
@@ -4427,7 +4531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>73</v>
       </c>
@@ -4444,7 +4548,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
@@ -4458,7 +4562,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
@@ -4469,7 +4573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
@@ -4480,7 +4584,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>25</v>
       </c>
@@ -4497,7 +4601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="7"/>
       <c r="C8" t="s">
@@ -4510,7 +4614,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>5</v>
       </c>
@@ -4590,7 +4694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>6</v>
       </c>
@@ -4604,7 +4708,7 @@
         <v>29.283333333000002</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>7</v>
       </c>
@@ -4618,7 +4722,7 @@
         <v>83.15</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>8</v>
       </c>
@@ -4632,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>9</v>
       </c>
@@ -4646,7 +4750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>10</v>
       </c>
@@ -4660,7 +4764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>11</v>
       </c>
@@ -4674,7 +4778,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>12</v>
       </c>
@@ -4688,7 +4792,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>13</v>
       </c>
@@ -4702,7 +4806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>14</v>
       </c>
@@ -4716,7 +4820,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>15</v>
       </c>
@@ -4730,7 +4834,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>16</v>
       </c>
@@ -4738,12 +4842,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="32" t="s">
         <v>5</v>
       </c>
@@ -4751,122 +4855,122 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>53</v>
       </c>
